--- a/Result/profitability/1307.xlsx
+++ b/Result/profitability/1307.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.91</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8325</v>
+        <v>0.7725</v>
       </c>
       <c r="N2" t="n">
-        <v>31.26</v>
+        <v>30.92875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7775000000000001</v>
+        <v>0.71875</v>
       </c>
       <c r="N3" t="n">
-        <v>29.69375</v>
+        <v>29.90875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0.74875</v>
+        <v>0.675</v>
       </c>
       <c r="N4" t="n">
-        <v>29.31875</v>
+        <v>28.98625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.70125</v>
+        <v>0.7775000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>27.335</v>
+        <v>27.2825</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.85375</v>
+        <v>0.7837499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>27.02375</v>
+        <v>26.95375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.76</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8174999999999999</v>
+        <v>0.7737499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>26.66875</v>
+        <v>26.45875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="N8" t="n">
-        <v>26.03375</v>
+        <v>25.745</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.82</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8049999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="N13" t="n">
         <v>26.85125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2711</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E75" t="n">
+        <v>821</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>288</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.61%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>297</v>
+      </c>
+      <c r="K75" t="n">
+        <v>195</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4948453608247423</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.310000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07088063823258672</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.083333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4199999999999982</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01368078175895759</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
